--- a/r5-core-27-IndexPage-Update/StructureDefinition-at-core-extendedContactDetail.xlsx
+++ b/r5-core-27-IndexPage-Update/StructureDefinition-at-core-extendedContactDetail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-16T15:46:32+00:00</t>
+    <t>2024-11-16T15:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-27-IndexPage-Update/StructureDefinition-at-core-extendedContactDetail.xlsx
+++ b/r5-core-27-IndexPage-Update/StructureDefinition-at-core-extendedContactDetail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-16T15:52:33+00:00</t>
+    <t>2024-11-16T16:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-27-IndexPage-Update/StructureDefinition-at-core-extendedContactDetail.xlsx
+++ b/r5-core-27-IndexPage-Update/StructureDefinition-at-core-extendedContactDetail.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="134">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-16T16:02:40+00:00</t>
+    <t>2025-01-17T11:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -390,21 +390,13 @@
 </t>
   </si>
   <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats)</t>
-  </si>
-  <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.
-The ISO21090-codedString may be used to provide a coded representation of the contents of strings in an Address.</t>
-  </si>
-  <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R5/location.html#) resource).</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}</t>
-  </si>
-  <si>
-    <t>n/a,AD</t>
+    <t>Address for the contact</t>
+  </si>
+  <si>
+    <t>Address for the contact.</t>
+  </si>
+  <si>
+    <t>More than 1 address would be for different purposes, and thus should be entered as a different entry,.</t>
   </si>
   <si>
     <t>ExtendedContactDetail.organization</t>
@@ -1551,7 +1543,7 @@
         <v>21</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="K8" t="s" s="2">
         <v>120</v>
@@ -1625,18 +1617,18 @@
         <v>21</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>125</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1659,17 +1651,17 @@
         <v>102</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="P9" t="s" s="2">
         <v>21</v>
@@ -1718,7 +1710,7 @@
         <v>21</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
@@ -1738,10 +1730,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1764,16 +1756,16 @@
         <v>102</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -1823,7 +1815,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
